--- a/data/trans_orig/POLIPATOLOGIA_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2007</t>
+          <t>Población con dos o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39298</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63561</t>
+          <t>65110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53881</t>
+          <t>53228</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82166</t>
+          <t>82256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99358</t>
+          <t>98128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135959</t>
+          <t>136086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209449</t>
+          <t>207900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233712</t>
+          <t>233827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178672</t>
+          <t>178582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206957</t>
+          <t>207610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>397889</t>
+          <t>397762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>434490</t>
+          <t>435720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72027</t>
+          <t>74655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107118</t>
+          <t>109089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182474</t>
+          <t>182952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>226360</t>
+          <t>225764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264803</t>
+          <t>264552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323000</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385957</t>
+          <t>383986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421048</t>
+          <t>418420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>277589</t>
+          <t>278185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321475</t>
+          <t>320997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674024</t>
+          <t>676198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732221</t>
+          <t>732472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41126</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66871</t>
+          <t>68825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86511</t>
+          <t>85260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120595</t>
+          <t>119191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135959</t>
+          <t>134242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178271</t>
+          <t>177124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251975</t>
+          <t>250021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277720</t>
+          <t>277493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214817</t>
+          <t>216221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248901</t>
+          <t>250152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>475987</t>
+          <t>477134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>518299</t>
+          <t>520016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>62261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89852</t>
+          <t>91759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97820</t>
+          <t>96746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133707</t>
+          <t>131640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165990</t>
+          <t>166149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210235</t>
+          <t>212916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268819</t>
+          <t>266912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299803</t>
+          <t>296410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>237749</t>
+          <t>239816</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273636</t>
+          <t>274710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>519892</t>
+          <t>517211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>564137</t>
+          <t>563978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>35910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>50433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78449</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72247</t>
+          <t>73424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107106</t>
+          <t>106286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166536</t>
+          <t>167398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185387</t>
+          <t>186022</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129219</t>
+          <t>130411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157871</t>
+          <t>157235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>303870</t>
+          <t>304690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338729</t>
+          <t>337552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39943</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64728</t>
+          <t>62969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>83348</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>113748</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128873</t>
+          <t>131257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169884</t>
+          <t>170045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206083</t>
+          <t>207842</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230868</t>
+          <t>232807</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160556</t>
+          <t>164396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193610</t>
+          <t>194796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379071</t>
+          <t>378910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420082</t>
+          <t>417698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101322</t>
+          <t>100410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140427</t>
+          <t>139277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165590</t>
+          <t>168330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211827</t>
+          <t>213260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277581</t>
+          <t>278139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340039</t>
+          <t>339212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>474600</t>
+          <t>475750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>513705</t>
+          <t>514617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>426392</t>
+          <t>424959</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>472629</t>
+          <t>469889</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>913207</t>
+          <t>914034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>975665</t>
+          <t>975107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>165262</t>
+          <t>164641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211426</t>
+          <t>208920</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264696</t>
+          <t>265108</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322414</t>
+          <t>320474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>443629</t>
+          <t>442784</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>518115</t>
+          <t>514339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>532369</t>
+          <t>534875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>578533</t>
+          <t>579154</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>461097</t>
+          <t>463037</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>518815</t>
+          <t>518403</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1009191</t>
+          <t>1012967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1083677</t>
+          <t>1084522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>602418</t>
+          <t>604686</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>688582</t>
+          <t>692536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1079246</t>
+          <t>1079368</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1194125</t>
+          <t>1189882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1699278</t>
+          <t>1710286</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1855089</t>
+          <t>1847148</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2587961</t>
+          <t>2584007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2674125</t>
+          <t>2671857</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2185072</t>
+          <t>2189315</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2299951</t>
+          <t>2299829</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4800652</t>
+          <t>4808593</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4956463</t>
+          <t>4945455</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2012</t>
+          <t>Población con dos o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53758</t>
+          <t>53483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84006</t>
+          <t>83031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100726</t>
+          <t>100894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135286</t>
+          <t>138408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164933</t>
+          <t>163008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211413</t>
+          <t>209520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210732</t>
+          <t>211707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>240980</t>
+          <t>241255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151959</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186519</t>
+          <t>186351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>370570</t>
+          <t>372463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>417050</t>
+          <t>418975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87405</t>
+          <t>89292</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127303</t>
+          <t>129528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160879</t>
+          <t>157744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203063</t>
+          <t>205380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255527</t>
+          <t>259519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>320153</t>
+          <t>316969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>378224</t>
+          <t>375999</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418122</t>
+          <t>416235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320702</t>
+          <t>318385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362886</t>
+          <t>366021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709139</t>
+          <t>712323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>773765</t>
+          <t>769773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74424</t>
+          <t>74361</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107864</t>
+          <t>108434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106803</t>
+          <t>106884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142634</t>
+          <t>144123</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189232</t>
+          <t>193587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239567</t>
+          <t>242926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216182</t>
+          <t>215612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>249622</t>
+          <t>249685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198386</t>
+          <t>196897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234217</t>
+          <t>234136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>425499</t>
+          <t>422140</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475834</t>
+          <t>471479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72833</t>
+          <t>71767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107554</t>
+          <t>106221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151565</t>
+          <t>151677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192459</t>
+          <t>191314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>231869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>287640</t>
+          <t>289533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266428</t>
+          <t>267761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301149</t>
+          <t>302215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196492</t>
+          <t>197637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237386</t>
+          <t>237274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>475293</t>
+          <t>473400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>529721</t>
+          <t>531064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>46530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74573</t>
+          <t>73917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115747</t>
+          <t>115798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143806</t>
+          <t>146001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168624</t>
+          <t>168874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210860</t>
+          <t>213575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138045</t>
+          <t>138701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165025</t>
+          <t>166088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75785</t>
+          <t>73590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103844</t>
+          <t>103793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221349</t>
+          <t>218634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263585</t>
+          <t>263335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75962</t>
+          <t>74364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106117</t>
+          <t>105972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111770</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145333</t>
+          <t>145997</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194532</t>
+          <t>196033</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242009</t>
+          <t>240862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167864</t>
+          <t>168009</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198019</t>
+          <t>199617</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134698</t>
+          <t>134034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>168261</t>
+          <t>167585</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312003</t>
+          <t>313150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>359480</t>
+          <t>357979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155123</t>
+          <t>152056</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202684</t>
+          <t>200560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>248348</t>
+          <t>250325</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301750</t>
+          <t>300936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417019</t>
+          <t>417119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>489022</t>
+          <t>489857</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>460104</t>
+          <t>462228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>507665</t>
+          <t>510732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>392103</t>
+          <t>392917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>445505</t>
+          <t>443528</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>867619</t>
+          <t>866784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>939622</t>
+          <t>939522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132221</t>
+          <t>130118</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177755</t>
+          <t>174944</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>219261</t>
+          <t>220195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>272602</t>
+          <t>271922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>368104</t>
+          <t>362265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>438989</t>
+          <t>435757</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>601343</t>
+          <t>604154</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>646877</t>
+          <t>648980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>551251</t>
+          <t>551931</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>604592</t>
+          <t>603658</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1163962</t>
+          <t>1167194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1234847</t>
+          <t>1240686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>787129</t>
+          <t>782057</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>888717</t>
+          <t>883353</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1320215</t>
+          <t>1319650</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1442583</t>
+          <t>1442411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2130636</t>
+          <t>2129607</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2286226</t>
+          <t>2282063</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2538062</t>
+          <t>2543426</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2639650</t>
+          <t>2644722</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2115726</t>
+          <t>2115898</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2238094</t>
+          <t>2238659</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4698862</t>
+          <t>4703025</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4854452</t>
+          <t>4855481</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2016</t>
+          <t>Población con dos o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57294</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87911</t>
+          <t>89552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>102617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137458</t>
+          <t>137049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169038</t>
+          <t>169548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215202</t>
+          <t>214507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205850</t>
+          <t>204209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236467</t>
+          <t>235410</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151245</t>
+          <t>151654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185456</t>
+          <t>186086</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367262</t>
+          <t>367957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>413426</t>
+          <t>412916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90874</t>
+          <t>92895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127070</t>
+          <t>130923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161832</t>
+          <t>163120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>207069</t>
+          <t>206654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263729</t>
+          <t>265612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325609</t>
+          <t>323069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375505</t>
+          <t>371652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411701</t>
+          <t>409680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316015</t>
+          <t>316430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361252</t>
+          <t>359964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700050</t>
+          <t>702590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>761930</t>
+          <t>760047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47464</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74894</t>
+          <t>74366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90242</t>
+          <t>91977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124903</t>
+          <t>126079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147146</t>
+          <t>145839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190588</t>
+          <t>191269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243671</t>
+          <t>244199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271101</t>
+          <t>270389</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211406</t>
+          <t>210230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246067</t>
+          <t>244332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464286</t>
+          <t>463605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507728</t>
+          <t>509035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89975</t>
+          <t>88904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127694</t>
+          <t>124347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146307</t>
+          <t>145152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186235</t>
+          <t>185617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244016</t>
+          <t>245760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>299234</t>
+          <t>303180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242270</t>
+          <t>245617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279989</t>
+          <t>281060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201048</t>
+          <t>201666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240976</t>
+          <t>242131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>458013</t>
+          <t>454067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>513231</t>
+          <t>511487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>36601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>61142</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74072</t>
+          <t>75582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102126</t>
+          <t>102300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119149</t>
+          <t>116938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154866</t>
+          <t>155133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150217</t>
+          <t>150079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174646</t>
+          <t>174620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116461</t>
+          <t>116287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144515</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274942</t>
+          <t>274675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310659</t>
+          <t>312870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48454</t>
+          <t>49304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76634</t>
+          <t>77727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77784</t>
+          <t>79191</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111129</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137750</t>
+          <t>138291</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180571</t>
+          <t>179973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186489</t>
+          <t>185396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214669</t>
+          <t>213819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>161986</t>
+          <t>162334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195331</t>
+          <t>193924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>355667</t>
+          <t>356265</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>398488</t>
+          <t>397947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121973</t>
+          <t>121237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166439</t>
+          <t>165631</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200592</t>
+          <t>202166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>248238</t>
+          <t>252414</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333638</t>
+          <t>338031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>400870</t>
+          <t>408012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>490119</t>
+          <t>490927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>534585</t>
+          <t>535321</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>443056</t>
+          <t>438880</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>490702</t>
+          <t>489128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>946982</t>
+          <t>939840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1014214</t>
+          <t>1009821</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>181526</t>
+          <t>182799</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>232795</t>
+          <t>231993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>263302</t>
+          <t>264606</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>321863</t>
+          <t>321330</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>465303</t>
+          <t>459689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>541476</t>
+          <t>536956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>545788</t>
+          <t>546590</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>597057</t>
+          <t>595784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>504304</t>
+          <t>504837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>562865</t>
+          <t>561561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1063274</t>
+          <t>1067794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1139447</t>
+          <t>1145061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>764151</t>
+          <t>759917</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>859191</t>
+          <t>856995</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1220979</t>
+          <t>1225763</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1338743</t>
+          <t>1344973</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2007492</t>
+          <t>2004080</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2164548</t>
+          <t>2159177</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2535159</t>
+          <t>2537355</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2630199</t>
+          <t>2634433</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2205799</t>
+          <t>2199569</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2323563</t>
+          <t>2318779</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4774344</t>
+          <t>4779715</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4931400</t>
+          <t>4934812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,12%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas en 2023</t>
+          <t>Población con dos o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>71545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106060</t>
+          <t>106669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85564</t>
+          <t>84946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111189</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163392</t>
+          <t>164863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209946</t>
+          <t>207500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205383</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>240643</t>
+          <t>239898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178446</t>
+          <t>178900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>204071</t>
+          <t>204689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>391131</t>
+          <t>393577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>437685</t>
+          <t>436214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112278</t>
+          <t>110483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159580</t>
+          <t>156644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184554</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224393</t>
+          <t>225950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>308052</t>
+          <t>307367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372684</t>
+          <t>369969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358810</t>
+          <t>361746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406112</t>
+          <t>407907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290576</t>
+          <t>289019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>330415</t>
+          <t>327656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>660675</t>
+          <t>663390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725307</t>
+          <t>725992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,26%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97132</t>
+          <t>97523</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129783</t>
+          <t>127759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147275</t>
+          <t>148408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179502</t>
+          <t>179191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254751</t>
+          <t>252093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299915</t>
+          <t>296585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>186267</t>
+          <t>188291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218918</t>
+          <t>218527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169626</t>
+          <t>169937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201853</t>
+          <t>200720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>365263</t>
+          <t>368593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410427</t>
+          <t>413085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93480</t>
+          <t>92152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132762</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197584</t>
+          <t>196773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>340899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305431</t>
+          <t>306728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>491334</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179795</t>
+          <t>182453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219077</t>
+          <t>220405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138444</t>
+          <t>134819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278134</t>
+          <t>278945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>296940</t>
+          <t>316457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482843</t>
+          <t>481546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>50290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69599</t>
+          <t>70312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>60919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142637</t>
+          <t>143242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113963</t>
+          <t>122208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198790</t>
+          <t>200356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109143</t>
+          <t>108430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129009</t>
+          <t>128452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116142</t>
+          <t>115537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201016</t>
+          <t>197860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>238731</t>
+          <t>237165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323558</t>
+          <t>315313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102700</t>
+          <t>102524</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131132</t>
+          <t>130727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115033</t>
+          <t>113522</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142002</t>
+          <t>140881</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>223326</t>
+          <t>223871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261907</t>
+          <t>263052</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138504</t>
+          <t>138909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166936</t>
+          <t>167112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115054</t>
+          <t>116175</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142023</t>
+          <t>143534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264785</t>
+          <t>263640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>303366</t>
+          <t>302821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>220537</t>
+          <t>219135</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>278424</t>
+          <t>274158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>516307</t>
+          <t>514008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>719717</t>
+          <t>726492</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>739848</t>
+          <t>734648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1098214</t>
+          <t>1064908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>72,27%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>345855</t>
+          <t>350121</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>403742</t>
+          <t>405144</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129548</t>
+          <t>122773</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332958</t>
+          <t>335257</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>375330</t>
+          <t>408636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>733696</t>
+          <t>738896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80471</t>
+          <t>85975</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>262365</t>
+          <t>263275</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>249865</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>295282</t>
+          <t>292902</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>289973</t>
+          <t>280408</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>549943</t>
+          <t>553534</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>666355</t>
+          <t>665445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>848249</t>
+          <t>842745</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>422449</t>
+          <t>424829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>467866</t>
+          <t>467281</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1096509</t>
+          <t>1092918</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1356479</t>
+          <t>1366044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>835717</t>
+          <t>805141</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1156801</t>
+          <t>1153971</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1683891</t>
+          <t>1684866</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2167780</t>
+          <t>2187398</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2608595</t>
+          <t>2625165</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3302182</t>
+          <t>3271032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2303016</t>
+          <t>2305846</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2624100</t>
+          <t>2654676</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1544500</t>
+          <t>1524882</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2028389</t>
+          <t>2027414</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3869915</t>
+          <t>3901065</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4563502</t>
+          <t>4546932</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>37383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65110</t>
+          <t>63702</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53228</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82256</t>
+          <t>82223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98128</t>
+          <t>98121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136086</t>
+          <t>137589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207900</t>
+          <t>209308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233827</t>
+          <t>235627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178582</t>
+          <t>178615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207610</t>
+          <t>207360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>397762</t>
+          <t>396259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435720</t>
+          <t>435727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74655</t>
+          <t>72971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109089</t>
+          <t>107272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182952</t>
+          <t>183036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225764</t>
+          <t>226862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>264552</t>
+          <t>266497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>320826</t>
+          <t>322685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383986</t>
+          <t>385803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418420</t>
+          <t>420104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278185</t>
+          <t>277087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320997</t>
+          <t>320913</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>676198</t>
+          <t>674339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732472</t>
+          <t>730527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41353</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68825</t>
+          <t>66886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85260</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119191</t>
+          <t>119474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134242</t>
+          <t>134780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177124</t>
+          <t>180042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250021</t>
+          <t>251960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277493</t>
+          <t>278843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>216221</t>
+          <t>215938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250152</t>
+          <t>248313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>477134</t>
+          <t>474216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>520016</t>
+          <t>519478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62261</t>
+          <t>59707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91759</t>
+          <t>89906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96746</t>
+          <t>98291</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>131824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166149</t>
+          <t>167764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212916</t>
+          <t>213402</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266912</t>
+          <t>268765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296410</t>
+          <t>298964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239816</t>
+          <t>239632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274710</t>
+          <t>273165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517211</t>
+          <t>516725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563978</t>
+          <t>562363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35910</t>
+          <t>37463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50433</t>
+          <t>51123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77257</t>
+          <t>78863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73424</t>
+          <t>70988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106286</t>
+          <t>106320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167398</t>
+          <t>165845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186022</t>
+          <t>185335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130411</t>
+          <t>128805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157235</t>
+          <t>156545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304690</t>
+          <t>304656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337552</t>
+          <t>339988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38004</t>
+          <t>39084</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62969</t>
+          <t>63770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83348</t>
+          <t>83864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113748</t>
+          <t>114727</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131257</t>
+          <t>126032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170045</t>
+          <t>167822</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207842</t>
+          <t>207041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232807</t>
+          <t>231727</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164396</t>
+          <t>163417</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194796</t>
+          <t>194280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>378910</t>
+          <t>381133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>417698</t>
+          <t>422923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>100460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139277</t>
+          <t>140796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168330</t>
+          <t>168634</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213260</t>
+          <t>213782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>278139</t>
+          <t>278494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339212</t>
+          <t>337502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475750</t>
+          <t>474231</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>514617</t>
+          <t>514567</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>424959</t>
+          <t>424437</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>469889</t>
+          <t>469585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>914034</t>
+          <t>915744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>975107</t>
+          <t>974752</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,78%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>164641</t>
+          <t>165035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>208920</t>
+          <t>212192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>265108</t>
+          <t>265868</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>320474</t>
+          <t>321857</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>442784</t>
+          <t>441934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>514339</t>
+          <t>516331</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>534875</t>
+          <t>531603</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>579154</t>
+          <t>578760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>463037</t>
+          <t>461654</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>518403</t>
+          <t>517643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1012967</t>
+          <t>1010975</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1084522</t>
+          <t>1085372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>604686</t>
+          <t>602391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>692536</t>
+          <t>693201</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1079368</t>
+          <t>1078673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1189882</t>
+          <t>1189146</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1710286</t>
+          <t>1711947</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1847148</t>
+          <t>1860969</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2584007</t>
+          <t>2583342</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2671857</t>
+          <t>2674152</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2189315</t>
+          <t>2190051</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2299829</t>
+          <t>2300524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4808593</t>
+          <t>4794772</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4945455</t>
+          <t>4943794</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53483</t>
+          <t>54091</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83031</t>
+          <t>82204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100894</t>
+          <t>100491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138408</t>
+          <t>136254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163008</t>
+          <t>163165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209520</t>
+          <t>210428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>211707</t>
+          <t>212534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241255</t>
+          <t>240647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148837</t>
+          <t>150991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186351</t>
+          <t>186754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>372463</t>
+          <t>371555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>418975</t>
+          <t>418818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89292</t>
+          <t>85831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129528</t>
+          <t>126406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157744</t>
+          <t>158863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205380</t>
+          <t>203622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259519</t>
+          <t>255829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316969</t>
+          <t>322158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375999</t>
+          <t>379121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416235</t>
+          <t>419696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318385</t>
+          <t>320143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366021</t>
+          <t>364902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>712323</t>
+          <t>707134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769773</t>
+          <t>773463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74361</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108434</t>
+          <t>108158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106884</t>
+          <t>106108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144123</t>
+          <t>142161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193587</t>
+          <t>191384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242926</t>
+          <t>241858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>215612</t>
+          <t>215888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>249685</t>
+          <t>248544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196897</t>
+          <t>198859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234136</t>
+          <t>234912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>422140</t>
+          <t>423208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>471479</t>
+          <t>473682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71767</t>
+          <t>71908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106221</t>
+          <t>105398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151677</t>
+          <t>151546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191314</t>
+          <t>191667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231869</t>
+          <t>234912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289533</t>
+          <t>286845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267761</t>
+          <t>268584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302215</t>
+          <t>302074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197637</t>
+          <t>197284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237274</t>
+          <t>237405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473400</t>
+          <t>476088</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>531064</t>
+          <t>528021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46530</t>
+          <t>47209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73917</t>
+          <t>75070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115798</t>
+          <t>115294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146001</t>
+          <t>143078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168874</t>
+          <t>167066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213575</t>
+          <t>208290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138701</t>
+          <t>137548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166088</t>
+          <t>165409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73590</t>
+          <t>76513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103793</t>
+          <t>104297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218634</t>
+          <t>223919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263335</t>
+          <t>265143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74364</t>
+          <t>75913</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105972</t>
+          <t>106486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>111764</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145997</t>
+          <t>144696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>196033</t>
+          <t>193472</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240862</t>
+          <t>240354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168009</t>
+          <t>167495</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199617</t>
+          <t>198068</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134034</t>
+          <t>135335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167585</t>
+          <t>168267</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313150</t>
+          <t>313658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>357979</t>
+          <t>360540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152056</t>
+          <t>153650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200560</t>
+          <t>201107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250325</t>
+          <t>250085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>300936</t>
+          <t>301182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417119</t>
+          <t>414596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>489857</t>
+          <t>487197</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>462228</t>
+          <t>461681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>510732</t>
+          <t>509138</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>392917</t>
+          <t>392671</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>443528</t>
+          <t>443768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>866784</t>
+          <t>869444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>939522</t>
+          <t>942045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130118</t>
+          <t>130696</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>174944</t>
+          <t>177800</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>220195</t>
+          <t>218593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>271922</t>
+          <t>272260</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>362265</t>
+          <t>366626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>435757</t>
+          <t>436011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>604154</t>
+          <t>601298</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>648980</t>
+          <t>648402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>551931</t>
+          <t>551593</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>603658</t>
+          <t>605260</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1167194</t>
+          <t>1166940</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1240686</t>
+          <t>1236325</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>782057</t>
+          <t>780825</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>883353</t>
+          <t>885096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1319650</t>
+          <t>1321643</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1442411</t>
+          <t>1434835</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2129607</t>
+          <t>2132730</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2282063</t>
+          <t>2295311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2543426</t>
+          <t>2541683</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2644722</t>
+          <t>2645954</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2115898</t>
+          <t>2123474</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2238659</t>
+          <t>2236666</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4703025</t>
+          <t>4689777</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4855481</t>
+          <t>4852358</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>58126</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89552</t>
+          <t>88503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102617</t>
+          <t>103796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137049</t>
+          <t>137092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169548</t>
+          <t>171633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214507</t>
+          <t>215685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204209</t>
+          <t>205258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235410</t>
+          <t>235635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151654</t>
+          <t>151611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186086</t>
+          <t>184907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367957</t>
+          <t>366779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>412916</t>
+          <t>410831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92895</t>
+          <t>91641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130923</t>
+          <t>128510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163120</t>
+          <t>162760</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206654</t>
+          <t>207068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265612</t>
+          <t>263822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323069</t>
+          <t>324757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371652</t>
+          <t>374065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409680</t>
+          <t>410934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316430</t>
+          <t>316016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359964</t>
+          <t>360324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702590</t>
+          <t>700902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>760047</t>
+          <t>761837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48176</t>
+          <t>49572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74366</t>
+          <t>74534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91977</t>
+          <t>91320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126079</t>
+          <t>126670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145839</t>
+          <t>146293</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191269</t>
+          <t>192549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244199</t>
+          <t>244031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270389</t>
+          <t>268993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210230</t>
+          <t>209639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244332</t>
+          <t>244989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>463605</t>
+          <t>462325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>509035</t>
+          <t>508581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>89973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124347</t>
+          <t>126394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145152</t>
+          <t>146517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185617</t>
+          <t>188220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245760</t>
+          <t>246586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303180</t>
+          <t>302089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245617</t>
+          <t>243570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>281060</t>
+          <t>279991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201666</t>
+          <t>199063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>242131</t>
+          <t>240766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>454067</t>
+          <t>455158</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>511487</t>
+          <t>510661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36601</t>
+          <t>37823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61142</t>
+          <t>60958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75582</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102300</t>
+          <t>103366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116938</t>
+          <t>118940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155133</t>
+          <t>156637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150079</t>
+          <t>150263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174620</t>
+          <t>173398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116287</t>
+          <t>115221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143005</t>
+          <t>144322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274675</t>
+          <t>273171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>312870</t>
+          <t>310868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>50176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77727</t>
+          <t>77746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79191</t>
+          <t>79167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110781</t>
+          <t>109990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138291</t>
+          <t>136707</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179973</t>
+          <t>181051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185396</t>
+          <t>185377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213819</t>
+          <t>212947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162334</t>
+          <t>163125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193924</t>
+          <t>193948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356265</t>
+          <t>355187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397947</t>
+          <t>399531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121237</t>
+          <t>122207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165631</t>
+          <t>164636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202166</t>
+          <t>198643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252414</t>
+          <t>248381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>338031</t>
+          <t>335626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408012</t>
+          <t>403114</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>490927</t>
+          <t>491922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>535321</t>
+          <t>534351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>438880</t>
+          <t>442913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>489128</t>
+          <t>492651</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>939840</t>
+          <t>944738</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1009821</t>
+          <t>1012226</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>182799</t>
+          <t>183121</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>231993</t>
+          <t>234476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264606</t>
+          <t>264254</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>321330</t>
+          <t>322735</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>459689</t>
+          <t>463881</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>536956</t>
+          <t>538496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>546590</t>
+          <t>544107</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>595784</t>
+          <t>595462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>504837</t>
+          <t>503432</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>561561</t>
+          <t>561913</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1067794</t>
+          <t>1066254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1145061</t>
+          <t>1140869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>759917</t>
+          <t>759512</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>856995</t>
+          <t>861636</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1225763</t>
+          <t>1218532</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1344973</t>
+          <t>1342725</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2004080</t>
+          <t>2009158</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2159177</t>
+          <t>2167617</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2537355</t>
+          <t>2532714</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2634433</t>
+          <t>2634838</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2199569</t>
+          <t>2201817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2318779</t>
+          <t>2326010</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4779715</t>
+          <t>4771275</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4934812</t>
+          <t>4929734</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>87268</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71545</t>
+          <t>71979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106669</t>
+          <t>103635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>97808</t>
+          <t>103917</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84946</t>
+          <t>90663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110735</t>
+          <t>116306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>185567</t>
+          <t>191185</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164863</t>
+          <t>171983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207500</t>
+          <t>211049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>223683</t>
+          <t>231577</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>215210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239898</t>
+          <t>246866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>191827</t>
+          <t>212144</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178900</t>
+          <t>199755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>204689</t>
+          <t>225398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>415510</t>
+          <t>443721</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>393577</t>
+          <t>423857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436214</t>
+          <t>462923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>133518</t>
+          <t>138156</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110483</t>
+          <t>115606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156644</t>
+          <t>162810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>205369</t>
+          <t>216973</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187313</t>
+          <t>197312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225950</t>
+          <t>237968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>338886</t>
+          <t>355129</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>307367</t>
+          <t>325705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369969</t>
+          <t>390979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>384872</t>
+          <t>392491</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361746</t>
+          <t>367837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407907</t>
+          <t>415041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>309600</t>
+          <t>329521</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289019</t>
+          <t>308526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327656</t>
+          <t>349182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>694473</t>
+          <t>722012</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>663390</t>
+          <t>686162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725992</t>
+          <t>751436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>112273</t>
+          <t>113388</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97523</t>
+          <t>97661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127759</t>
+          <t>129210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>163465</t>
+          <t>168565</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148408</t>
+          <t>151541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179191</t>
+          <t>183490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>275738</t>
+          <t>281953</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252093</t>
+          <t>261248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296585</t>
+          <t>304514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>203777</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188291</t>
+          <t>186783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218527</t>
+          <t>218332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>185663</t>
+          <t>187816</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169937</t>
+          <t>172891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200720</t>
+          <t>204840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>389440</t>
+          <t>390422</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>368593</t>
+          <t>367861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>413085</t>
+          <t>411127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>111584</t>
+          <t>123671</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92152</t>
+          <t>102242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>149713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>250516</t>
+          <t>199328</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196773</t>
+          <t>179405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>340899</t>
+          <t>218862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>362099</t>
+          <t>323000</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>306728</t>
+          <t>292418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>471817</t>
+          <t>349884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>200973</t>
+          <t>249474</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182453</t>
+          <t>223432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220405</t>
+          <t>270903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>225202</t>
+          <t>222633</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134819</t>
+          <t>203099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278945</t>
+          <t>242556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>426175</t>
+          <t>472107</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316457</t>
+          <t>445223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>481546</t>
+          <t>502689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59513</t>
+          <t>64127</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>53209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70312</t>
+          <t>74852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>112999</t>
+          <t>119015</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60919</t>
+          <t>108319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143242</t>
+          <t>129918</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>172512</t>
+          <t>183141</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122208</t>
+          <t>167615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200356</t>
+          <t>199942</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>119229</t>
+          <t>141538</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108430</t>
+          <t>130813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128452</t>
+          <t>152456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>145780</t>
+          <t>109903</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115537</t>
+          <t>99000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197860</t>
+          <t>120599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>265009</t>
+          <t>251441</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237165</t>
+          <t>234640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315313</t>
+          <t>266967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>116316</t>
+          <t>115244</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102524</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130727</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>127028</t>
+          <t>129910</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113522</t>
+          <t>117325</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>140881</t>
+          <t>144036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>243344</t>
+          <t>245154</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>223871</t>
+          <t>226413</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>263052</t>
+          <t>264231</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>153320</t>
+          <t>155463</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138909</t>
+          <t>140255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167112</t>
+          <t>168822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>130028</t>
+          <t>133840</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116175</t>
+          <t>119714</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143534</t>
+          <t>146425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>283348</t>
+          <t>289303</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263640</t>
+          <t>270226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302821</t>
+          <t>308044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>247221</t>
+          <t>289551</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>219135</t>
+          <t>259472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>274158</t>
+          <t>319613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>602836</t>
+          <t>478989</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>514008</t>
+          <t>453046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>726492</t>
+          <t>505314</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>850057</t>
+          <t>768539</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>734648</t>
+          <t>728908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1064908</t>
+          <t>812430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>377058</t>
+          <t>430136</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>350121</t>
+          <t>400074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>405144</t>
+          <t>460215</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246429</t>
+          <t>293068</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122773</t>
+          <t>266743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>335257</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>623487</t>
+          <t>723205</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408636</t>
+          <t>679314</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>738896</t>
+          <t>762836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>186494</t>
+          <t>209413</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85975</t>
+          <t>185829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>263275</t>
+          <t>233599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>271949</t>
+          <t>307446</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250450</t>
+          <t>285825</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>292902</t>
+          <t>332767</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>458443</t>
+          <t>516859</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>280408</t>
+          <t>484801</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>553534</t>
+          <t>554120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>742226</t>
+          <t>588659</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>665445</t>
+          <t>564473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>842745</t>
+          <t>612243</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>445782</t>
+          <t>523885</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>424829</t>
+          <t>498564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>467281</t>
+          <t>545506</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1188009</t>
+          <t>1112544</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1092918</t>
+          <t>1075283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1366044</t>
+          <t>1144602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1054679</t>
+          <t>1140819</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>805141</t>
+          <t>1085220</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1153971</t>
+          <t>1205055</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1831969</t>
+          <t>1724142</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1684866</t>
+          <t>1673647</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2187398</t>
+          <t>1779174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2886648</t>
+          <t>2864962</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2625165</t>
+          <t>2775215</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3271032</t>
+          <t>2946273</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2405138</t>
+          <t>2391943</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2305846</t>
+          <t>2327707</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2654676</t>
+          <t>2447542</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1880311</t>
+          <t>2012812</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1524882</t>
+          <t>1957780</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2027414</t>
+          <t>2063307</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4285449</t>
+          <t>4404754</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3901065</t>
+          <t>4323443</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4546932</t>
+          <t>4494501</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
